--- a/artfynd/A 14693-2026 artfynd.xlsx
+++ b/artfynd/A 14693-2026 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133330830</v>
+        <v>133330713</v>
       </c>
       <c r="B2" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576867</v>
+        <v>576878</v>
       </c>
       <c r="R2" t="n">
-        <v>7079177</v>
+        <v>7079193</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133330713</v>
+        <v>133330830</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576878</v>
+        <v>576867</v>
       </c>
       <c r="R3" t="n">
-        <v>7079193</v>
+        <v>7079177</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,11 +872,11 @@
         <v>133330869</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -969,11 +969,11 @@
         <v>133330891</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
